--- a/design/tables/StaffForm.xlsx
+++ b/design/tables/StaffForm.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StaffForm" sheetId="1" r:id="R6f480a5cc9494954"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StaffForm" sheetId="1" r:id="Rcfc8985a47284df8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -27,8 +27,18 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF243C32"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF243C32"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -45,6 +55,11 @@
         <x:fgColor rgb="FF35584D"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -52,7 +67,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -75,6 +90,17 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -451,194 +477,514 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="8" t="n">
+      <x:c r="A6" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="str">
+      <x:c r="B6" s="11" t="str">
         <x:v>sprout_heavy</x:v>
       </x:c>
-      <x:c r="C6" s="8" t="str">
+      <x:c r="C6" s="11" t="str">
         <x:v>sprout_heavy</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="str">
+      <x:c r="D6" s="11" t="str">
         <x:v>sprout_heavy</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="str">
+      <x:c r="E6" s="11" t="str">
         <x:v>sprout_heavy</x:v>
       </x:c>
-      <x:c r="F6" s="8" t="str">
+      <x:c r="F6" s="11" t="str">
         <x:v>evolution.sprout_heavy.story</x:v>
       </x:c>
-      <x:c r="G6" s="8" t="str">
+      <x:c r="G6" s="11" t="str">
         <x:v>branch.sprout_heavy.summary</x:v>
       </x:c>
-      <x:c r="H6" s="8" t="str">
+      <x:c r="H6" s="11" t="str">
         <x:v>branch.sprout_heavy.tradeoff</x:v>
       </x:c>
-      <x:c r="I6" s="8" t="n">
+      <x:c r="I6" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J6" s="8" t="n">
+      <x:c r="J6" s="11" t="n">
         <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
-      <x:c r="A7" s="8" t="n">
+      <x:c r="A7" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="str">
+      <x:c r="B7" s="11" t="str">
         <x:v>sprout_burst</x:v>
       </x:c>
-      <x:c r="C7" s="8" t="str">
+      <x:c r="C7" s="11" t="str">
         <x:v>sprout_burst</x:v>
       </x:c>
-      <x:c r="D7" s="8" t="str">
+      <x:c r="D7" s="11" t="str">
         <x:v>sprout_burst</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="str">
+      <x:c r="E7" s="11" t="str">
         <x:v>sprout_burst</x:v>
       </x:c>
-      <x:c r="F7" s="8" t="str">
+      <x:c r="F7" s="11" t="str">
         <x:v>evolution.sprout_burst.story</x:v>
       </x:c>
-      <x:c r="G7" s="8" t="str">
+      <x:c r="G7" s="11" t="str">
         <x:v>branch.sprout_burst.summary</x:v>
       </x:c>
-      <x:c r="H7" s="8" t="str">
+      <x:c r="H7" s="11" t="str">
         <x:v>branch.sprout_burst.tradeoff</x:v>
       </x:c>
-      <x:c r="I7" s="8" t="n">
+      <x:c r="I7" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J7" s="8" t="n">
+      <x:c r="J7" s="11" t="n">
         <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
-      <x:c r="A8" s="8" t="n">
+      <x:c r="A8" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="str">
+      <x:c r="B8" s="11" t="str">
         <x:v>frost_deep</x:v>
       </x:c>
-      <x:c r="C8" s="8" t="str">
+      <x:c r="C8" s="11" t="str">
         <x:v>frost_deep</x:v>
       </x:c>
-      <x:c r="D8" s="8" t="str">
+      <x:c r="D8" s="11" t="str">
         <x:v>frost_deep</x:v>
       </x:c>
-      <x:c r="E8" s="8" t="str">
+      <x:c r="E8" s="11" t="str">
         <x:v>frost_deep</x:v>
       </x:c>
-      <x:c r="F8" s="8" t="str">
+      <x:c r="F8" s="11" t="str">
         <x:v>evolution.frost_deep.story</x:v>
       </x:c>
-      <x:c r="G8" s="8" t="str">
+      <x:c r="G8" s="11" t="str">
         <x:v>branch.frost_deep.summary</x:v>
       </x:c>
-      <x:c r="H8" s="8" t="str">
+      <x:c r="H8" s="11" t="str">
         <x:v>branch.frost_deep.tradeoff</x:v>
       </x:c>
-      <x:c r="I8" s="8" t="n">
+      <x:c r="I8" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J8" s="8" t="n">
+      <x:c r="J8" s="11" t="n">
         <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
-      <x:c r="A9" s="8" t="n">
+      <x:c r="A9" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B9" s="8" t="str">
+      <x:c r="B9" s="11" t="str">
         <x:v>frost_dual</x:v>
       </x:c>
-      <x:c r="C9" s="8" t="str">
+      <x:c r="C9" s="11" t="str">
         <x:v>frost_dual</x:v>
       </x:c>
-      <x:c r="D9" s="8" t="str">
+      <x:c r="D9" s="11" t="str">
         <x:v>frost_dual</x:v>
       </x:c>
-      <x:c r="E9" s="8" t="str">
+      <x:c r="E9" s="11" t="str">
         <x:v>frost_dual</x:v>
       </x:c>
-      <x:c r="F9" s="8" t="str">
+      <x:c r="F9" s="11" t="str">
         <x:v>evolution.frost_dual.story</x:v>
       </x:c>
-      <x:c r="G9" s="8" t="str">
+      <x:c r="G9" s="11" t="str">
         <x:v>branch.frost_dual.summary</x:v>
       </x:c>
-      <x:c r="H9" s="8" t="str">
+      <x:c r="H9" s="11" t="str">
         <x:v>branch.frost_dual.tradeoff</x:v>
       </x:c>
-      <x:c r="I9" s="8" t="n">
+      <x:c r="I9" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J9" s="8" t="n">
+      <x:c r="J9" s="11" t="n">
         <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
-      <x:c r="A10" s="8" t="n">
+      <x:c r="A10" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B10" s="8" t="str">
+      <x:c r="B10" s="11" t="str">
         <x:v>bloom_focus</x:v>
       </x:c>
-      <x:c r="C10" s="8" t="str">
+      <x:c r="C10" s="11" t="str">
         <x:v>bloom_focus</x:v>
       </x:c>
-      <x:c r="D10" s="8" t="str">
+      <x:c r="D10" s="11" t="str">
         <x:v>bloom_focus</x:v>
       </x:c>
-      <x:c r="E10" s="8" t="str">
+      <x:c r="E10" s="11" t="str">
         <x:v>bloom_focus</x:v>
       </x:c>
-      <x:c r="F10" s="8" t="str">
+      <x:c r="F10" s="11" t="str">
         <x:v>evolution.bloom_focus.story</x:v>
       </x:c>
-      <x:c r="G10" s="8" t="str">
+      <x:c r="G10" s="11" t="str">
         <x:v>branch.bloom_focus.summary</x:v>
       </x:c>
-      <x:c r="H10" s="8" t="str">
+      <x:c r="H10" s="11" t="str">
         <x:v>branch.bloom_focus.tradeoff</x:v>
       </x:c>
-      <x:c r="I10" s="8" t="n">
+      <x:c r="I10" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J10" s="8" t="n">
+      <x:c r="J10" s="11" t="n">
         <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
-      <x:c r="A11" s="8" t="n">
+      <x:c r="A11" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B11" s="8" t="str">
+      <x:c r="B11" s="11" t="str">
         <x:v>bloom_wide</x:v>
       </x:c>
-      <x:c r="C11" s="8" t="str">
+      <x:c r="C11" s="11" t="str">
         <x:v>bloom_wide</x:v>
       </x:c>
-      <x:c r="D11" s="8" t="str">
+      <x:c r="D11" s="11" t="str">
         <x:v>bloom_wide</x:v>
       </x:c>
-      <x:c r="E11" s="8" t="str">
+      <x:c r="E11" s="11" t="str">
         <x:v>bloom_wide</x:v>
       </x:c>
-      <x:c r="F11" s="8" t="str">
+      <x:c r="F11" s="11" t="str">
         <x:v>evolution.bloom_wide.story</x:v>
       </x:c>
-      <x:c r="G11" s="8" t="str">
+      <x:c r="G11" s="11" t="str">
         <x:v>branch.bloom_wide.summary</x:v>
       </x:c>
-      <x:c r="H11" s="8" t="str">
+      <x:c r="H11" s="11" t="str">
         <x:v>branch.bloom_wide.tradeoff</x:v>
       </x:c>
-      <x:c r="I11" s="8" t="n">
+      <x:c r="I11" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J11" s="8" t="n">
+      <x:c r="J11" s="11" t="n">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="48" customHeight="1">
+      <x:c r="A12" s="13" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B12" s="13" t="str">
+        <x:v>scope_precision</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="str">
+        <x:v>scope_precision</x:v>
+      </x:c>
+      <x:c r="D12" s="13" t="str">
+        <x:v>scope_precision</x:v>
+      </x:c>
+      <x:c r="E12" s="13" t="str">
+        <x:v>scope_precision</x:v>
+      </x:c>
+      <x:c r="F12" s="13" t="str">
+        <x:v>branch.scope_precision.story</x:v>
+      </x:c>
+      <x:c r="G12" s="13" t="str">
+        <x:v>branch.scope_precision.summary</x:v>
+      </x:c>
+      <x:c r="H12" s="13" t="str">
+        <x:v>branch.scope_precision.tradeoff</x:v>
+      </x:c>
+      <x:c r="I12" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J12" s="13" t="n">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="48" customHeight="1">
+      <x:c r="A13" s="13" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B13" s="13" t="str">
+        <x:v>scope_pierce</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="str">
+        <x:v>scope_pierce</x:v>
+      </x:c>
+      <x:c r="D13" s="13" t="str">
+        <x:v>scope_pierce</x:v>
+      </x:c>
+      <x:c r="E13" s="13" t="str">
+        <x:v>scope_pierce</x:v>
+      </x:c>
+      <x:c r="F13" s="13" t="str">
+        <x:v>branch.scope_pierce.story</x:v>
+      </x:c>
+      <x:c r="G13" s="13" t="str">
+        <x:v>branch.scope_pierce.summary</x:v>
+      </x:c>
+      <x:c r="H13" s="13" t="str">
+        <x:v>branch.scope_pierce.tradeoff</x:v>
+      </x:c>
+      <x:c r="I13" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J13" s="13" t="n">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="48" customHeight="1">
+      <x:c r="A14" s="13" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B14" s="13" t="str">
+        <x:v>spark_focus</x:v>
+      </x:c>
+      <x:c r="C14" s="13" t="str">
+        <x:v>spark_focus</x:v>
+      </x:c>
+      <x:c r="D14" s="13" t="str">
+        <x:v>spark_focus</x:v>
+      </x:c>
+      <x:c r="E14" s="13" t="str">
+        <x:v>spark_focus</x:v>
+      </x:c>
+      <x:c r="F14" s="13" t="str">
+        <x:v>branch.spark_focus.story</x:v>
+      </x:c>
+      <x:c r="G14" s="13" t="str">
+        <x:v>branch.spark_focus.summary</x:v>
+      </x:c>
+      <x:c r="H14" s="13" t="str">
+        <x:v>branch.spark_focus.tradeoff</x:v>
+      </x:c>
+      <x:c r="I14" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J14" s="13" t="n">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="48" customHeight="1">
+      <x:c r="A15" s="13" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B15" s="13" t="str">
+        <x:v>spark_chain</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="str">
+        <x:v>spark_chain</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="str">
+        <x:v>spark_chain</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="str">
+        <x:v>spark_chain</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="str">
+        <x:v>branch.spark_chain.story</x:v>
+      </x:c>
+      <x:c r="G15" s="13" t="str">
+        <x:v>branch.spark_chain.summary</x:v>
+      </x:c>
+      <x:c r="H15" s="13" t="str">
+        <x:v>branch.spark_chain.tradeoff</x:v>
+      </x:c>
+      <x:c r="I15" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J15" s="13" t="n">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="48" customHeight="1">
+      <x:c r="A16" s="13" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="str">
+        <x:v>ember_scorch</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="str">
+        <x:v>ember_scorch</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="str">
+        <x:v>ember_scorch</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="str">
+        <x:v>ember_scorch</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="str">
+        <x:v>branch.ember_scorch.story</x:v>
+      </x:c>
+      <x:c r="G16" s="13" t="str">
+        <x:v>branch.ember_scorch.summary</x:v>
+      </x:c>
+      <x:c r="H16" s="13" t="str">
+        <x:v>branch.ember_scorch.tradeoff</x:v>
+      </x:c>
+      <x:c r="I16" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J16" s="13" t="n">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="48" customHeight="1">
+      <x:c r="A17" s="13" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="str">
+        <x:v>ember_burst</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="str">
+        <x:v>ember_burst</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="str">
+        <x:v>ember_burst</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="str">
+        <x:v>ember_burst</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="str">
+        <x:v>branch.ember_burst.story</x:v>
+      </x:c>
+      <x:c r="G17" s="13" t="str">
+        <x:v>branch.ember_burst.summary</x:v>
+      </x:c>
+      <x:c r="H17" s="13" t="str">
+        <x:v>branch.ember_burst.tradeoff</x:v>
+      </x:c>
+      <x:c r="I17" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J17" s="13" t="n">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="48" customHeight="1">
+      <x:c r="A18" s="13" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="str">
+        <x:v>mint_focus</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="str">
+        <x:v>mint_focus</x:v>
+      </x:c>
+      <x:c r="D18" s="13" t="str">
+        <x:v>mint_focus</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="str">
+        <x:v>mint_focus</x:v>
+      </x:c>
+      <x:c r="F18" s="13" t="str">
+        <x:v>branch.mint_focus.story</x:v>
+      </x:c>
+      <x:c r="G18" s="13" t="str">
+        <x:v>branch.mint_focus.summary</x:v>
+      </x:c>
+      <x:c r="H18" s="13" t="str">
+        <x:v>branch.mint_focus.tradeoff</x:v>
+      </x:c>
+      <x:c r="I18" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J18" s="13" t="n">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="48" customHeight="1">
+      <x:c r="A19" s="13" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B19" s="13" t="str">
+        <x:v>mint_dual</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="str">
+        <x:v>mint_dual</x:v>
+      </x:c>
+      <x:c r="D19" s="13" t="str">
+        <x:v>mint_dual</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="str">
+        <x:v>mint_dual</x:v>
+      </x:c>
+      <x:c r="F19" s="13" t="str">
+        <x:v>branch.mint_dual.story</x:v>
+      </x:c>
+      <x:c r="G19" s="13" t="str">
+        <x:v>branch.mint_dual.summary</x:v>
+      </x:c>
+      <x:c r="H19" s="13" t="str">
+        <x:v>branch.mint_dual.tradeoff</x:v>
+      </x:c>
+      <x:c r="I19" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J19" s="13" t="n">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="48" customHeight="1">
+      <x:c r="A20" s="13" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B20" s="13" t="str">
+        <x:v>fan_spread</x:v>
+      </x:c>
+      <x:c r="C20" s="13" t="str">
+        <x:v>fan_spread</x:v>
+      </x:c>
+      <x:c r="D20" s="13" t="str">
+        <x:v>fan_spread</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="str">
+        <x:v>fan_spread</x:v>
+      </x:c>
+      <x:c r="F20" s="13" t="str">
+        <x:v>branch.fan_spread.story</x:v>
+      </x:c>
+      <x:c r="G20" s="13" t="str">
+        <x:v>branch.fan_spread.summary</x:v>
+      </x:c>
+      <x:c r="H20" s="13" t="str">
+        <x:v>branch.fan_spread.tradeoff</x:v>
+      </x:c>
+      <x:c r="I20" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J20" s="13" t="n">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="48" customHeight="1">
+      <x:c r="A21" s="13" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="str">
+        <x:v>fan_volley</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="str">
+        <x:v>fan_volley</x:v>
+      </x:c>
+      <x:c r="D21" s="13" t="str">
+        <x:v>fan_volley</x:v>
+      </x:c>
+      <x:c r="E21" s="13" t="str">
+        <x:v>fan_volley</x:v>
+      </x:c>
+      <x:c r="F21" s="13" t="str">
+        <x:v>branch.fan_volley.story</x:v>
+      </x:c>
+      <x:c r="G21" s="13" t="str">
+        <x:v>branch.fan_volley.summary</x:v>
+      </x:c>
+      <x:c r="H21" s="13" t="str">
+        <x:v>branch.fan_volley.tradeoff</x:v>
+      </x:c>
+      <x:c r="I21" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J21" s="13" t="n">
         <x:v>88</x:v>
       </x:c>
     </x:row>
